--- a/ig/DM-MAI-2026/ASS-A28-TypeDiplome-Diplome-Profession-EPARS.xlsx
+++ b/ig/DM-MAI-2026/ASS-A28-TypeDiplome-Diplome-Profession-EPARS.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="104">
   <si>
     <t>Property</t>
   </si>
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240726120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -776,7 +776,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1303,7 +1303,7 @@
         <v>33</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E40" s="2"/>
     </row>
@@ -1316,7 +1316,7 @@
         <v>33</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E41" s="2"/>
     </row>
@@ -1329,7 +1329,7 @@
         <v>33</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E42" s="2"/>
     </row>
@@ -1342,7 +1342,7 @@
         <v>33</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E43" s="2"/>
     </row>
@@ -1355,7 +1355,7 @@
         <v>33</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E44" s="2"/>
     </row>
@@ -1368,7 +1368,7 @@
         <v>33</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
     </row>
@@ -1381,7 +1381,7 @@
         <v>33</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E46" s="2"/>
     </row>
@@ -1394,7 +1394,7 @@
         <v>33</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E47" s="2"/>
     </row>
@@ -1407,7 +1407,7 @@
         <v>33</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E48" s="2"/>
     </row>
@@ -1420,7 +1420,7 @@
         <v>33</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E49" s="2"/>
     </row>
@@ -1433,7 +1433,7 @@
         <v>33</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E50" s="2"/>
     </row>
@@ -1446,7 +1446,7 @@
         <v>33</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E51" s="2"/>
     </row>
@@ -1459,9 +1459,35 @@
         <v>33</v>
       </c>
       <c r="D52" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B53" s="2"/>
+      <c r="C53" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B54" s="2"/>
+      <c r="C54" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D54" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="E52" s="2"/>
+      <c r="E54" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/DM-MAI-2026/ASS-A28-TypeDiplome-Diplome-Profession-EPARS.xlsx
+++ b/ig/DM-MAI-2026/ASS-A28-TypeDiplome-Diplome-Profession-EPARS.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="104">
   <si>
     <t>Property</t>
   </si>
@@ -776,7 +776,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1329,7 +1329,7 @@
         <v>33</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E42" s="2"/>
     </row>
@@ -1355,7 +1355,7 @@
         <v>33</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E44" s="2"/>
     </row>
@@ -1368,7 +1368,7 @@
         <v>33</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E45" s="2"/>
     </row>
@@ -1381,7 +1381,7 @@
         <v>33</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
     </row>
@@ -1394,7 +1394,7 @@
         <v>33</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E47" s="2"/>
     </row>
@@ -1407,7 +1407,7 @@
         <v>33</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E48" s="2"/>
     </row>
@@ -1420,7 +1420,7 @@
         <v>33</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E49" s="2"/>
     </row>
@@ -1433,7 +1433,7 @@
         <v>33</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E50" s="2"/>
     </row>
@@ -1446,7 +1446,7 @@
         <v>33</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E51" s="2"/>
     </row>
@@ -1459,7 +1459,7 @@
         <v>33</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E52" s="2"/>
     </row>
@@ -1472,7 +1472,7 @@
         <v>33</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E53" s="2"/>
     </row>
@@ -1485,9 +1485,22 @@
         <v>33</v>
       </c>
       <c r="D54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="E54" s="2"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B55" s="2"/>
+      <c r="C55" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D55" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="E54" s="2"/>
+      <c r="E55" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
